--- a/data/trans_orig/P21D4_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P21D4_2023-Provincia-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, necesitándolo, no pudo recibir atención médica mental (psicólogo) en 2023</t>
+          <t>Población que, necesitándolo, no pudo recibir atención médica mental (psicólogo) en 2023 (tasa de respuesta: 99,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,7 +730,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>147329</t>
+          <t>147487</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -745,7 +745,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,61%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>118434</t>
+          <t>118653</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>124343</t>
+          <t>124559</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>93,93%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>270096</t>
+          <t>269648</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>277738</t>
+          <t>277973</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>99,07%</t>
         </is>
       </c>
     </row>
@@ -848,7 +848,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6937</t>
+          <t>6779</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1813</t>
+          <t>1661</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7761</t>
+          <t>7351</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2701</t>
+          <t>2577</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>10369</t>
+          <t>10962</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,91%</t>
         </is>
       </c>
     </row>
@@ -956,97 +956,97 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>1921</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>1,25%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="R6" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>1036</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>0,82%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>1392</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1069,97 +1069,97 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>166</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>1921</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>833</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>0,13%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>1,25%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>0,66%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>166</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>942</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,13%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>872</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,06%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>0,75%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>166</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>920</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,06%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,31%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>165775</t>
+          <t>165861</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>193562</t>
+          <t>193747</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>78,47%</t>
+          <t>78,51%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>91,62%</t>
+          <t>91,7%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>196132</t>
+          <t>197009</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>214872</t>
+          <t>215588</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>83,06%</t>
+          <t>83,43%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>91,0%</t>
+          <t>91,3%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>371660</t>
+          <t>372968</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>406422</t>
+          <t>404066</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>83,07%</t>
+          <t>83,36%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>90,84%</t>
+          <t>90,31%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13722</t>
+          <t>14028</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>41848</t>
+          <t>40953</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>19,38%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>15070</t>
+          <t>15180</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>32484</t>
+          <t>33265</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>14,09%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>33050</t>
+          <t>33264</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>65623</t>
+          <t>64221</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>14,35%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>882</t>
+          <t>794</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8145</t>
+          <t>9243</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2332</t>
+          <t>2229</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9760</t>
+          <t>9678</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>4145</t>
+          <t>4200</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>15298</t>
+          <t>14415</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,22%</t>
         </is>
       </c>
     </row>
@@ -1643,7 +1643,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5976</t>
+          <t>5227</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>164</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5353</t>
+          <t>4518</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1693,7 +1693,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>751</t>
+          <t>698</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>7562</t>
+          <t>7001</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,56%</t>
         </is>
       </c>
     </row>
@@ -1868,7 +1868,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>83548</t>
+          <t>84716</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1883,7 +1883,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,03%</t>
+          <t>89,26%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>125947</t>
+          <t>125553</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>136647</t>
+          <t>136446</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,54%</t>
+          <t>86,27%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,89%</t>
+          <t>93,75%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>214360</t>
+          <t>213787</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>228454</t>
+          <t>228201</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,15%</t>
+          <t>88,91%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>94,9%</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>560</t>
+          <t>574</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>10609</t>
+          <t>9255</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3751</t>
+          <t>3666</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>11838</t>
+          <t>11963</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>6376</t>
+          <t>6372</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>17846</t>
+          <t>18185</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,56%</t>
         </is>
       </c>
     </row>
@@ -2094,97 +2094,97 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>1211</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>1596</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>3753</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>0,83%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>1,68%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>2,58%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="R16" s="2" t="inlineStr">
         <is>
           <t>1211</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
+      <c r="S16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>3613</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,83%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>3800</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>0,5%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>2,48%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>1211</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>4268</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,5%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,58%</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4222</t>
+          <t>4189</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2227,7 +2227,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2547</t>
+          <t>2564</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>10157</t>
+          <t>10175</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2833</t>
+          <t>3026</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>11440</t>
+          <t>11430</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,75%</t>
         </is>
       </c>
     </row>
@@ -2437,12 +2437,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>119060</t>
+          <t>120168</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>135424</t>
+          <t>135313</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>84,21%</t>
+          <t>85,0%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>95,71%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>222799</t>
+          <t>222972</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>240929</t>
+          <t>240594</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>90,36%</t>
+          <t>90,43%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>348966</t>
+          <t>348853</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>373323</t>
+          <t>373575</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>89,95%</t>
+          <t>89,93%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>96,23%</t>
+          <t>96,3%</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4021</t>
+          <t>4384</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>18754</t>
+          <t>18784</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>5107</t>
+          <t>5482</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>22836</t>
+          <t>22480</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>12663</t>
+          <t>12499</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>35739</t>
+          <t>34678</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>8,94%</t>
         </is>
       </c>
     </row>
@@ -2668,7 +2668,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3638</t>
+          <t>4079</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2683,7 +2683,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>3557</t>
+          <t>3325</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2718,7 +2718,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2738,7 +2738,7 @@
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>4847</t>
+          <t>5014</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2753,7 +2753,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,29%</t>
         </is>
       </c>
     </row>
@@ -2781,7 +2781,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>6648</t>
+          <t>6235</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,62 +2811,62 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>1684</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>1696</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>6469</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>0,43%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>0,69%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>1684</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>7332</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>0,43%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,67%</t>
         </is>
       </c>
     </row>
@@ -3006,12 +3006,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>61497</t>
+          <t>61355</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>68889</t>
+          <t>68894</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3021,12 +3021,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>86,98%</t>
+          <t>86,78%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3041,12 +3041,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>59789</t>
+          <t>60320</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>68712</t>
+          <t>68758</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>83,78%</t>
+          <t>84,53%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>96,35%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3076,12 +3076,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>125112</t>
+          <t>126054</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>136210</t>
+          <t>136385</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>88,07%</t>
+          <t>88,73%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>96,0%</t>
         </is>
       </c>
     </row>
@@ -3119,12 +3119,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>707</t>
+          <t>752</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>8488</t>
+          <t>8796</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3154,12 +3154,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1485</t>
+          <t>1392</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>10467</t>
+          <t>10132</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3189,12 +3189,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3549</t>
+          <t>3327</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>13721</t>
+          <t>13322</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,38%</t>
         </is>
       </c>
     </row>
@@ -3237,7 +3237,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3908</t>
+          <t>4405</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3252,7 +3252,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3272,7 +3272,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2135</t>
+          <t>2102</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3287,7 +3287,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3302,12 +3302,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>420</t>
+          <t>409</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4844</t>
+          <t>4514</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,18%</t>
         </is>
       </c>
     </row>
@@ -3345,12 +3345,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1243</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3360,12 +3360,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>345</t>
+          <t>348</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3136</t>
+          <t>3173</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3395,12 +3395,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>351</t>
+          <t>346</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>3026</t>
+          <t>2946</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3430,12 +3430,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,07%</t>
         </is>
       </c>
     </row>
@@ -3575,12 +3575,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>119565</t>
+          <t>119635</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>125121</t>
+          <t>125123</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3590,7 +3590,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>101438</t>
+          <t>101641</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>107813</t>
+          <t>108160</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>91,43%</t>
+          <t>91,61%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,48%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3645,12 +3645,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>224088</t>
+          <t>224210</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>232394</t>
+          <t>232467</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>94,73%</t>
+          <t>94,79%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,28%</t>
         </is>
       </c>
     </row>
@@ -3688,12 +3688,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>473</t>
+          <t>471</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>6029</t>
+          <t>5959</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>2901</t>
+          <t>2570</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>9380</t>
+          <t>8925</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3738,12 +3738,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>3697</t>
+          <t>3821</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>12053</t>
+          <t>11911</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3773,12 +3773,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,04%</t>
         </is>
       </c>
     </row>
@@ -3801,97 +3801,97 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>351</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>1354</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>2092</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>0,32%</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>1,08%</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>1,89%</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K31" s="2" t="inlineStr">
+      <c r="R31" s="2" t="inlineStr">
         <is>
           <t>351</t>
         </is>
       </c>
-      <c r="L31" s="2" t="inlineStr">
+      <c r="S31" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M31" s="2" t="inlineStr">
-        <is>
-          <t>1830</t>
-        </is>
-      </c>
-      <c r="N31" s="2" t="inlineStr">
-        <is>
-          <t>0,32%</t>
-        </is>
-      </c>
-      <c r="O31" s="2" t="inlineStr">
+      <c r="T31" s="2" t="inlineStr">
+        <is>
+          <t>1837</t>
+        </is>
+      </c>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>0,15%</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P31" s="2" t="inlineStr">
-        <is>
-          <t>1,65%</t>
-        </is>
-      </c>
-      <c r="Q31" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R31" s="2" t="inlineStr">
-        <is>
-          <t>351</t>
-        </is>
-      </c>
-      <c r="S31" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T31" s="2" t="inlineStr">
-        <is>
-          <t>1773</t>
-        </is>
-      </c>
-      <c r="U31" s="2" t="inlineStr">
-        <is>
-          <t>0,15%</t>
-        </is>
-      </c>
-      <c r="V31" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,78%</t>
         </is>
       </c>
     </row>
@@ -3914,97 +3914,97 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>1354</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>1,08%</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K32" s="2" t="inlineStr">
+      <c r="R32" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L32" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr">
-        <is>
-          <t>1059</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr">
+      <c r="S32" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T32" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U32" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O32" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P32" s="2" t="inlineStr">
-        <is>
-          <t>0,95%</t>
-        </is>
-      </c>
-      <c r="Q32" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R32" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S32" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T32" s="2" t="inlineStr">
-        <is>
-          <t>1201</t>
-        </is>
-      </c>
-      <c r="U32" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>280190</t>
+          <t>281199</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>300129</t>
+          <t>300325</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>89,88%</t>
+          <t>90,2%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,34%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>260550</t>
+          <t>261044</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>282353</t>
+          <t>282747</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>84,91%</t>
+          <t>85,07%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>92,02%</t>
+          <t>92,14%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>547914</t>
+          <t>547277</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>579205</t>
+          <t>578442</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>88,57%</t>
+          <t>88,47%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>93,63%</t>
+          <t>93,51%</t>
         </is>
       </c>
     </row>
@@ -4257,12 +4257,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>8530</t>
+          <t>9022</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>27572</t>
+          <t>28252</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4272,12 +4272,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4292,12 +4292,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>16971</t>
+          <t>16490</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>35619</t>
+          <t>34976</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4327,12 +4327,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>28385</t>
+          <t>29080</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>55379</t>
+          <t>56907</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>9,2%</t>
         </is>
       </c>
     </row>
@@ -4370,12 +4370,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>1092</t>
+          <t>1049</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>10054</t>
+          <t>9117</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4385,12 +4385,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4405,12 +4405,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>2065</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>17327</t>
+          <t>14506</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4425,7 +4425,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4440,12 +4440,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>4369</t>
+          <t>3952</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>21081</t>
+          <t>18982</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,07%</t>
         </is>
       </c>
     </row>
@@ -4483,12 +4483,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>2092</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4498,12 +4498,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4518,12 +4518,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>1240</t>
+          <t>1189</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>9915</t>
+          <t>9620</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4533,12 +4533,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4553,12 +4553,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>1123</t>
+          <t>1170</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>9268</t>
+          <t>10331</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4568,12 +4568,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,67%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>100951</t>
+          <t>100077</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>527324</t>
+          <t>527164</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>18,07%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,17%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>312848</t>
+          <t>313581</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>329348</t>
+          <t>329855</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>89,82%</t>
+          <t>90,03%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>94,7%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>258676</t>
+          <t>288962</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>848989</t>
+          <t>848883</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>28,67%</t>
+          <t>32,03%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>94,09%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>20706</t>
+          <t>20620</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>451286</t>
+          <t>452186</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>81,47%</t>
+          <t>81,63%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>16540</t>
+          <t>16036</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>32525</t>
+          <t>31783</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>45531</t>
+          <t>45519</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>639062</t>
+          <t>608868</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4916,7 +4916,7 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>70,83%</t>
+          <t>67,48%</t>
         </is>
       </c>
     </row>
@@ -4944,7 +4944,7 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>11087</t>
+          <t>11299</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4959,7 +4959,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4979,7 +4979,7 @@
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>4845</t>
+          <t>4722</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4994,7 +4994,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5009,12 +5009,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>1277</t>
+          <t>1265</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>12188</t>
+          <t>12355</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5029,7 +5029,7 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,37%</t>
         </is>
       </c>
     </row>
@@ -5052,97 +5052,97 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>1319</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>3183</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>4549</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>0,38%</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>0,57%</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>1,31%</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K42" s="2" t="inlineStr">
+      <c r="R42" s="2" t="inlineStr">
         <is>
           <t>1319</t>
         </is>
       </c>
-      <c r="L42" s="2" t="inlineStr">
+      <c r="S42" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M42" s="2" t="inlineStr">
-        <is>
-          <t>4185</t>
-        </is>
-      </c>
-      <c r="N42" s="2" t="inlineStr">
-        <is>
-          <t>0,38%</t>
-        </is>
-      </c>
-      <c r="O42" s="2" t="inlineStr">
+      <c r="T42" s="2" t="inlineStr">
+        <is>
+          <t>5438</t>
+        </is>
+      </c>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
+          <t>0,15%</t>
+        </is>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P42" s="2" t="inlineStr">
-        <is>
-          <t>1,2%</t>
-        </is>
-      </c>
-      <c r="Q42" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R42" s="2" t="inlineStr">
-        <is>
-          <t>1319</t>
-        </is>
-      </c>
-      <c r="S42" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T42" s="2" t="inlineStr">
-        <is>
-          <t>5161</t>
-        </is>
-      </c>
-      <c r="U42" s="2" t="inlineStr">
-        <is>
-          <t>0,15%</t>
-        </is>
-      </c>
-      <c r="V42" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,6%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>802902</t>
+          <t>828706</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>1565734</t>
+          <t>1568296</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>48,26%</t>
+          <t>49,81%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>94,26%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>1439505</t>
+          <t>1439125</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>1483893</t>
+          <t>1482893</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>90,42%</t>
+          <t>90,4%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>93,21%</t>
+          <t>93,14%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>2126661</t>
+          <t>2136189</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>3024900</t>
+          <t>3025062</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5367,7 +5367,7 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>65,32%</t>
+          <t>65,61%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>80366</t>
+          <t>78781</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>854336</t>
+          <t>825986</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>51,35%</t>
+          <t>49,65%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>83613</t>
+          <t>86001</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>123125</t>
+          <t>122883</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>184223</t>
+          <t>184734</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>1093766</t>
+          <t>1078507</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>33,59%</t>
+          <t>33,13%</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>5424</t>
+          <t>5547</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>20295</t>
+          <t>21209</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5528,7 +5528,7 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>9243</t>
+          <t>9070</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>25749</t>
+          <t>25261</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>17796</t>
+          <t>17485</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>41642</t>
+          <t>39242</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,21%</t>
         </is>
       </c>
     </row>
@@ -5621,12 +5621,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>676</t>
+          <t>796</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>8695</t>
+          <t>9442</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5636,12 +5636,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,05%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>8255</t>
+          <t>7828</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>20783</t>
+          <t>21203</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>9917</t>
+          <t>10170</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>24816</t>
+          <t>26447</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,81%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P21D4_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P21D4_2023-Provincia-trans_orig.xlsx
@@ -725,27 +725,27 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>152374</t>
+          <t>152581</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>147487</t>
+          <t>148267</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>154266</t>
+          <t>154287</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,89%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>122452</t>
+          <t>134233</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>118653</t>
+          <t>130370</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>124559</t>
+          <t>136678</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>93,99%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>274826</t>
+          <t>286814</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>269648</t>
+          <t>281177</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>277973</t>
+          <t>289539</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>98,82%</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1892</t>
+          <t>1706</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -848,12 +848,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6779</t>
+          <t>6020</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3699</t>
+          <t>3967</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1661</t>
+          <t>1853</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7351</t>
+          <t>7465</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>5591</t>
+          <t>5673</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2577</t>
+          <t>3005</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>10962</t>
+          <t>11097</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,79%</t>
         </is>
       </c>
     </row>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>166</t>
+          <t>509</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>833</t>
+          <t>2806</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>166</t>
+          <t>509</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>872</t>
+          <t>2494</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,85%</t>
         </is>
       </c>
     </row>
@@ -1177,17 +1177,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>154266</t>
+          <t>154287</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>154266</t>
+          <t>154287</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>154266</t>
+          <t>154287</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1212,17 +1212,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>126317</t>
+          <t>138709</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>126317</t>
+          <t>138709</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>126317</t>
+          <t>138709</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>280583</t>
+          <t>292996</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>280583</t>
+          <t>292996</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>280583</t>
+          <t>292996</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>182804</t>
+          <t>193856</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>165861</t>
+          <t>178415</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>193747</t>
+          <t>204315</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>86,52%</t>
+          <t>87,43%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>78,51%</t>
+          <t>80,46%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>91,7%</t>
+          <t>92,15%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>207730</t>
+          <t>220691</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>197009</t>
+          <t>209791</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>215588</t>
+          <t>229174</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>87,97%</t>
+          <t>87,74%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>83,43%</t>
+          <t>83,41%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>91,3%</t>
+          <t>91,11%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>390534</t>
+          <t>414546</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>372968</t>
+          <t>396342</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>404066</t>
+          <t>429244</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>87,29%</t>
+          <t>87,59%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>83,36%</t>
+          <t>83,75%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>90,31%</t>
+          <t>90,7%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>24439</t>
+          <t>23855</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14028</t>
+          <t>14338</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>40953</t>
+          <t>39244</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>21917</t>
+          <t>22188</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>15180</t>
+          <t>15141</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>33265</t>
+          <t>32036</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>46356</t>
+          <t>46043</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>33264</t>
+          <t>32989</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>64221</t>
+          <t>64090</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>13,54%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3026</t>
+          <t>3027</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>794</t>
+          <t>914</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9243</t>
+          <t>8380</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4986</t>
+          <t>6722</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2229</t>
+          <t>3331</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9678</t>
+          <t>12507</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>8012</t>
+          <t>9750</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>4200</t>
+          <t>5217</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>14415</t>
+          <t>16312</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,45%</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1004</t>
+          <t>995</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1643,12 +1643,12 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5227</t>
+          <t>4331</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>1927</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>582</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>4518</t>
+          <t>5524</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>2504</t>
+          <t>2921</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>698</t>
+          <t>978</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>7001</t>
+          <t>8014</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,69%</t>
         </is>
       </c>
     </row>
@@ -1746,17 +1746,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>211273</t>
+          <t>221732</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>211273</t>
+          <t>221732</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>211273</t>
+          <t>221732</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>236133</t>
+          <t>251528</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>236133</t>
+          <t>251528</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>236133</t>
+          <t>251528</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>447406</t>
+          <t>473260</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>447406</t>
+          <t>473260</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>447406</t>
+          <t>473260</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>90581</t>
+          <t>88954</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>84716</t>
+          <t>82026</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>93670</t>
+          <t>91842</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,59%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,26%</t>
+          <t>88,15%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>131902</t>
+          <t>132531</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>125553</t>
+          <t>126424</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>136446</t>
+          <t>137437</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>90,63%</t>
+          <t>90,56%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,27%</t>
+          <t>86,39%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>93,91%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>222483</t>
+          <t>221485</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>213787</t>
+          <t>213730</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>228201</t>
+          <t>227876</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>92,53%</t>
+          <t>92,52%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,91%</t>
+          <t>89,28%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,9%</t>
+          <t>95,19%</t>
         </is>
       </c>
     </row>
@@ -1976,32 +1976,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3638</t>
+          <t>3440</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>574</t>
+          <t>576</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>9255</t>
+          <t>10450</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2011,32 +2011,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>7090</t>
+          <t>7227</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3666</t>
+          <t>3804</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>11963</t>
+          <t>12039</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2046,17 +2046,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>10728</t>
+          <t>10667</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>6372</t>
+          <t>5860</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>18185</t>
+          <t>17919</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,49%</t>
         </is>
       </c>
     </row>
@@ -2124,7 +2124,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1211</t>
+          <t>1212</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -2134,7 +2134,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3753</t>
+          <t>3734</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1211</t>
+          <t>1212</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
@@ -2169,12 +2169,12 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3800</t>
+          <t>4062</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,7%</t>
         </is>
       </c>
     </row>
@@ -2202,7 +2202,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>693</t>
+          <t>660</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -2212,12 +2212,12 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4189</t>
+          <t>2988</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -2227,7 +2227,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,17 +2237,17 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>5339</t>
+          <t>5372</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2564</t>
+          <t>2438</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>10175</t>
+          <t>9972</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,27 +2277,27 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3026</t>
+          <t>2706</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>11430</t>
+          <t>10923</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,56%</t>
         </is>
       </c>
     </row>
@@ -2315,17 +2315,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>94912</t>
+          <t>93054</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>94912</t>
+          <t>93054</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>94912</t>
+          <t>93054</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2350,17 +2350,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>145541</t>
+          <t>146342</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>145541</t>
+          <t>146342</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>145541</t>
+          <t>146342</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>240453</t>
+          <t>239396</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>240453</t>
+          <t>239396</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>240453</t>
+          <t>239396</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2432,32 +2432,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>129274</t>
+          <t>161728</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>120168</t>
+          <t>151367</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>135313</t>
+          <t>168206</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>91,44%</t>
+          <t>92,7%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>85,0%</t>
+          <t>86,76%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2467,32 +2467,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>231930</t>
+          <t>185641</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>222972</t>
+          <t>178545</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>240594</t>
+          <t>191573</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>94,07%</t>
+          <t>92,13%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>90,43%</t>
+          <t>88,6%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>95,07%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>361205</t>
+          <t>347369</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>348853</t>
+          <t>334439</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>373575</t>
+          <t>355845</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>93,11%</t>
+          <t>92,39%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>89,93%</t>
+          <t>88,95%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>94,65%</t>
         </is>
       </c>
     </row>
@@ -2545,32 +2545,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>9668</t>
+          <t>10281</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4384</t>
+          <t>4631</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>18784</t>
+          <t>20589</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2580,32 +2580,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>14002</t>
+          <t>15235</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>5482</t>
+          <t>9452</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>22480</t>
+          <t>21928</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>23670</t>
+          <t>25516</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>12499</t>
+          <t>17661</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>34678</t>
+          <t>37930</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>10,09%</t>
         </is>
       </c>
     </row>
@@ -2658,7 +2658,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>750</t>
+          <t>720</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -2668,12 +2668,12 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4079</t>
+          <t>3981</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -2683,7 +2683,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2693,7 +2693,7 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>628</t>
+          <t>632</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
@@ -2703,12 +2703,12 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>3325</t>
+          <t>3509</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
@@ -2718,7 +2718,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2728,7 +2728,7 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1378</t>
+          <t>1352</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
@@ -2738,7 +2738,7 @@
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>5014</t>
+          <t>4407</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2753,7 +2753,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,17%</t>
         </is>
       </c>
     </row>
@@ -2771,7 +2771,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>1684</t>
+          <t>1731</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -2781,12 +2781,12 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>6235</t>
+          <t>6638</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1684</t>
+          <t>1731</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
@@ -2851,12 +2851,12 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>6469</t>
+          <t>6738</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,79%</t>
         </is>
       </c>
     </row>
@@ -2884,17 +2884,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>141377</t>
+          <t>174460</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>141377</t>
+          <t>174460</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>141377</t>
+          <t>174460</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,17 +2919,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>246560</t>
+          <t>201508</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>246560</t>
+          <t>201508</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>246560</t>
+          <t>201508</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>387937</t>
+          <t>375968</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>387937</t>
+          <t>375968</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>387937</t>
+          <t>375968</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3001,32 +3001,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>66259</t>
+          <t>79732</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>61355</t>
+          <t>74032</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>68894</t>
+          <t>82618</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>93,71%</t>
+          <t>94,45%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>86,78%</t>
+          <t>87,69%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3036,32 +3036,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>66019</t>
+          <t>73395</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>60320</t>
+          <t>66342</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>68758</t>
+          <t>76353</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>92,51%</t>
+          <t>92,45%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>84,53%</t>
+          <t>83,57%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3071,32 +3071,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>132278</t>
+          <t>153127</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>126054</t>
+          <t>145004</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>136385</t>
+          <t>157851</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>93,11%</t>
+          <t>93,48%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>88,73%</t>
+          <t>88,52%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>96,36%</t>
         </is>
       </c>
     </row>
@@ -3114,32 +3114,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>3246</t>
+          <t>3426</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>752</t>
+          <t>1223</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>8796</t>
+          <t>8993</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3149,32 +3149,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>3765</t>
+          <t>4300</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1392</t>
+          <t>1674</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>10132</t>
+          <t>11613</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3184,32 +3184,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>7011</t>
+          <t>7726</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3327</t>
+          <t>3656</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>13322</t>
+          <t>15189</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,27%</t>
         </is>
       </c>
     </row>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>1199</t>
+          <t>1263</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>4405</t>
+          <t>4424</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -3252,7 +3252,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3262,7 +3262,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>412</t>
+          <t>432</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
@@ -3272,12 +3272,12 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2102</t>
+          <t>2319</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
@@ -3287,7 +3287,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3297,32 +3297,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1612</t>
+          <t>1695</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>409</t>
+          <t>429</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4514</t>
+          <t>4571</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>2,79%</t>
         </is>
       </c>
     </row>
@@ -3375,32 +3375,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1166</t>
+          <t>1258</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>348</t>
+          <t>372</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3173</t>
+          <t>3412</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3410,32 +3410,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1166</t>
+          <t>1258</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>346</t>
+          <t>373</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>2946</t>
+          <t>4045</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,47%</t>
         </is>
       </c>
     </row>
@@ -3453,17 +3453,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>70704</t>
+          <t>84421</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>70704</t>
+          <t>84421</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>70704</t>
+          <t>84421</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>71362</t>
+          <t>79385</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>71362</t>
+          <t>79385</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>71362</t>
+          <t>79385</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>142066</t>
+          <t>163806</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>142066</t>
+          <t>163806</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>142066</t>
+          <t>163806</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3570,32 +3570,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>123755</t>
+          <t>125046</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>119635</t>
+          <t>121954</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>125123</t>
+          <t>126383</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>96,14%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,63%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3605,32 +3605,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>105382</t>
+          <t>107507</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>101641</t>
+          <t>103399</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>108160</t>
+          <t>110458</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>91,61%</t>
+          <t>90,93%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3640,32 +3640,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>229138</t>
+          <t>232553</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>224210</t>
+          <t>227889</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>232467</t>
+          <t>235994</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>94,79%</t>
+          <t>94,73%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,1%</t>
         </is>
       </c>
     </row>
@@ -3683,32 +3683,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1839</t>
+          <t>1800</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>471</t>
+          <t>463</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>5959</t>
+          <t>4892</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3718,32 +3718,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>5219</t>
+          <t>5838</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>2570</t>
+          <t>2938</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>8925</t>
+          <t>9850</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3753,32 +3753,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>7058</t>
+          <t>7638</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>3821</t>
+          <t>4263</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>11911</t>
+          <t>12566</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,22%</t>
         </is>
       </c>
     </row>
@@ -3831,7 +3831,7 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>351</t>
+          <t>371</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
@@ -3841,12 +3841,12 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>2092</t>
+          <t>1760</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>351</t>
+          <t>371</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
@@ -3876,7 +3876,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>1837</t>
+          <t>1874</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -4022,17 +4022,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>125594</t>
+          <t>126846</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>125594</t>
+          <t>126846</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>125594</t>
+          <t>126846</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4057,17 +4057,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>110952</t>
+          <t>113716</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>110952</t>
+          <t>113716</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>110952</t>
+          <t>113716</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4092,17 +4092,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>236546</t>
+          <t>240562</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>236546</t>
+          <t>240562</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>236546</t>
+          <t>240562</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4139,32 +4139,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>292139</t>
+          <t>329617</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>281199</t>
+          <t>315257</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>300325</t>
+          <t>338689</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>93,71%</t>
+          <t>93,43%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>90,2%</t>
+          <t>89,36%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>96,0%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4174,32 +4174,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>272758</t>
+          <t>318025</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>261044</t>
+          <t>305244</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>282747</t>
+          <t>328670</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>88,89%</t>
+          <t>89,29%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>85,07%</t>
+          <t>85,7%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>92,14%</t>
+          <t>92,28%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4209,32 +4209,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>564898</t>
+          <t>647641</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>547277</t>
+          <t>629560</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>578442</t>
+          <t>661524</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>91,32%</t>
+          <t>91,35%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>88,47%</t>
+          <t>88,8%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>93,51%</t>
+          <t>93,31%</t>
         </is>
       </c>
     </row>
@@ -4252,32 +4252,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>16100</t>
+          <t>19641</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>9022</t>
+          <t>11612</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>28252</t>
+          <t>34219</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4287,32 +4287,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>24628</t>
+          <t>28562</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>16490</t>
+          <t>19965</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>34976</t>
+          <t>40533</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4322,32 +4322,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>40728</t>
+          <t>48204</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>29080</t>
+          <t>35500</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>56907</t>
+          <t>63469</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>8,95%</t>
         </is>
       </c>
     </row>
@@ -4365,32 +4365,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>3497</t>
+          <t>3549</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>1049</t>
+          <t>1121</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>9117</t>
+          <t>10476</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4400,32 +4400,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>5892</t>
+          <t>5835</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>2089</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>14506</t>
+          <t>14299</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4435,32 +4435,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>9389</t>
+          <t>9384</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>3952</t>
+          <t>4409</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>18982</t>
+          <t>18468</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>2,6%</t>
         </is>
       </c>
     </row>
@@ -4513,32 +4513,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>3576</t>
+          <t>3757</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>1189</t>
+          <t>710</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>9620</t>
+          <t>10028</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4548,32 +4548,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>3576</t>
+          <t>3757</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>1170</t>
+          <t>729</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>10331</t>
+          <t>10394</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,47%</t>
         </is>
       </c>
     </row>
@@ -4591,17 +4591,17 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>311736</t>
+          <t>352807</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>311736</t>
+          <t>352807</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>311736</t>
+          <t>352807</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4626,17 +4626,17 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>306854</t>
+          <t>356179</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>306854</t>
+          <t>356179</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>306854</t>
+          <t>356179</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4661,17 +4661,17 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>618590</t>
+          <t>708986</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>618590</t>
+          <t>708986</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>618590</t>
+          <t>708986</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4708,32 +4708,32 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>292294</t>
+          <t>340361</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>100077</t>
+          <t>328765</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>527164</t>
+          <t>348261</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>52,77%</t>
+          <t>94,37%</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>91,15%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4743,32 +4743,32 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>322764</t>
+          <t>377222</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>313581</t>
+          <t>365250</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>329855</t>
+          <t>385198</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>92,66%</t>
+          <t>92,68%</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>90,03%</t>
+          <t>89,74%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>94,64%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4778,32 +4778,32 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>615057</t>
+          <t>717582</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>288962</t>
+          <t>703817</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>848883</t>
+          <t>729266</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t>68,17%</t>
+          <t>93,48%</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>32,03%</t>
+          <t>91,68%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>94,09%</t>
+          <t>95,0%</t>
         </is>
       </c>
     </row>
@@ -4821,32 +4821,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>258269</t>
+          <t>16591</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>20620</t>
+          <t>9717</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>452186</t>
+          <t>26916</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>46,63%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>81,63%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4856,32 +4856,32 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>22853</t>
+          <t>26640</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>16036</t>
+          <t>18847</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>31783</t>
+          <t>38162</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4891,32 +4891,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>281122</t>
+          <t>43231</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>45519</t>
+          <t>31577</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>608868</t>
+          <t>55567</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>31,16%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>67,48%</t>
+          <t>7,24%</t>
         </is>
       </c>
     </row>
@@ -4934,67 +4934,67 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>3352</t>
+          <t>3715</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
+          <t>791</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>11889</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>1,03%</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>0,22%</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>3,3%</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>1686</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>11299</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>0,61%</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>6099</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>0,41%</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>2,04%</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K41" s="2" t="inlineStr">
-        <is>
-          <t>1379</t>
-        </is>
-      </c>
-      <c r="L41" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr">
-        <is>
-          <t>4722</t>
-        </is>
-      </c>
-      <c r="N41" s="2" t="inlineStr">
-        <is>
-          <t>0,4%</t>
-        </is>
-      </c>
-      <c r="O41" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5004,32 +5004,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>4732</t>
+          <t>5401</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>1265</t>
+          <t>1777</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>12355</t>
+          <t>12846</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,67%</t>
         </is>
       </c>
     </row>
@@ -5082,7 +5082,7 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>1319</t>
+          <t>1458</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
@@ -5092,12 +5092,12 @@
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>4549</t>
+          <t>5146</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
@@ -5107,7 +5107,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5117,7 +5117,7 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>1319</t>
+          <t>1458</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
@@ -5127,12 +5127,12 @@
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>5438</t>
+          <t>5282</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
@@ -5142,7 +5142,7 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,69%</t>
         </is>
       </c>
     </row>
@@ -5160,17 +5160,17 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>553916</t>
+          <t>360667</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>553916</t>
+          <t>360667</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>553916</t>
+          <t>360667</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5195,17 +5195,17 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>348315</t>
+          <t>407006</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>348315</t>
+          <t>407006</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>348315</t>
+          <t>407006</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5230,17 +5230,17 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>902230</t>
+          <t>767673</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>902230</t>
+          <t>767673</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>902230</t>
+          <t>767673</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5277,32 +5277,32 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>1329482</t>
+          <t>1471874</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>828706</t>
+          <t>1445332</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>1568296</t>
+          <t>1492768</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>79,91%</t>
+          <t>93,85%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>49,81%</t>
+          <t>92,16%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>94,26%</t>
+          <t>95,19%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5312,32 +5312,32 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>1460937</t>
+          <t>1549245</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>1439125</t>
+          <t>1527462</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>1482893</t>
+          <t>1568694</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>91,77%</t>
+          <t>91,43%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>90,4%</t>
+          <t>90,15%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>93,14%</t>
+          <t>92,58%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5347,32 +5347,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>2790419</t>
+          <t>3021119</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>2136189</t>
+          <t>2987565</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>3025062</t>
+          <t>3047101</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>85,71%</t>
+          <t>92,6%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>65,61%</t>
+          <t>91,57%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>92,91%</t>
+          <t>93,39%</t>
         </is>
       </c>
     </row>
@@ -5390,32 +5390,32 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>319090</t>
+          <t>80741</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>78781</t>
+          <t>61816</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>825986</t>
+          <t>106024</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>49,65%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -5425,32 +5425,32 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>103172</t>
+          <t>113957</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>86001</t>
+          <t>96882</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>122883</t>
+          <t>133502</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5460,32 +5460,32 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>422262</t>
+          <t>194698</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>184734</t>
+          <t>168733</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>1078507</t>
+          <t>223399</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>33,13%</t>
+          <t>6,85%</t>
         </is>
       </c>
     </row>
@@ -5503,32 +5503,32 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>11825</t>
+          <t>12274</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>5547</t>
+          <t>6079</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>21209</t>
+          <t>21208</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5538,32 +5538,32 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>14859</t>
+          <t>16890</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>9070</t>
+          <t>10710</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>25261</t>
+          <t>27816</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5573,32 +5573,32 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>26684</t>
+          <t>29164</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>17485</t>
+          <t>20270</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>39242</t>
+          <t>43107</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,32%</t>
         </is>
       </c>
     </row>
@@ -5616,32 +5616,32 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>3381</t>
+          <t>3385</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>796</t>
+          <t>1149</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>9442</t>
+          <t>8584</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5651,67 +5651,67 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>13066</t>
+          <t>14282</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>7828</t>
+          <t>8822</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>21203</t>
+          <t>21994</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
+          <t>0,84%</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>0,52%</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>1,3%</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="R47" s="2" t="inlineStr">
+        <is>
+          <t>17667</t>
+        </is>
+      </c>
+      <c r="S47" s="2" t="inlineStr">
+        <is>
+          <t>11739</t>
+        </is>
+      </c>
+      <c r="T47" s="2" t="inlineStr">
+        <is>
+          <t>26607</t>
+        </is>
+      </c>
+      <c r="U47" s="2" t="inlineStr">
+        <is>
+          <t>0,54%</t>
+        </is>
+      </c>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>0,36%</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
           <t>0,82%</t>
-        </is>
-      </c>
-      <c r="O47" s="2" t="inlineStr">
-        <is>
-          <t>0,49%</t>
-        </is>
-      </c>
-      <c r="P47" s="2" t="inlineStr">
-        <is>
-          <t>1,33%</t>
-        </is>
-      </c>
-      <c r="Q47" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="R47" s="2" t="inlineStr">
-        <is>
-          <t>16447</t>
-        </is>
-      </c>
-      <c r="S47" s="2" t="inlineStr">
-        <is>
-          <t>10170</t>
-        </is>
-      </c>
-      <c r="T47" s="2" t="inlineStr">
-        <is>
-          <t>26447</t>
-        </is>
-      </c>
-      <c r="U47" s="2" t="inlineStr">
-        <is>
-          <t>0,51%</t>
-        </is>
-      </c>
-      <c r="V47" s="2" t="inlineStr">
-        <is>
-          <t>0,31%</t>
-        </is>
-      </c>
-      <c r="W47" s="2" t="inlineStr">
-        <is>
-          <t>0,81%</t>
         </is>
       </c>
     </row>
@@ -5729,17 +5729,17 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>1663778</t>
+          <t>1568274</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>1663778</t>
+          <t>1568274</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>1663778</t>
+          <t>1568274</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5764,17 +5764,17 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>1592034</t>
+          <t>1694374</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>1592034</t>
+          <t>1694374</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>1592034</t>
+          <t>1694374</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5799,17 +5799,17 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>3255812</t>
+          <t>3262648</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>3255812</t>
+          <t>3262648</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>3255812</t>
+          <t>3262648</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
